--- a/tippelag.xlsx
+++ b/tippelag.xlsx
@@ -1,19 +1,3 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sammenlagt" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Historikk" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
-</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -406,332 +390,4 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Navn</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Poeng</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Rette</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>520</v>
-      </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>KAF</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>480</v>
-      </c>
-      <c r="C3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>JH</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>440</v>
-      </c>
-      <c r="C4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AHH</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>400</v>
-      </c>
-      <c r="C5" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LEV</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>400</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>UTG</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>400</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TOH</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>360</v>
-      </c>
-      <c r="C8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ØG</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>320</v>
-      </c>
-      <c r="C9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EB</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>240</v>
-      </c>
-      <c r="C10" t="n">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Navn</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Uke</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Poeng</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Rette</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AHH</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>400</v>
-      </c>
-      <c r="D2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EB</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>240</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>JH</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>440</v>
-      </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>KAF</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>480</v>
-      </c>
-      <c r="D5" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LEV</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>400</v>
-      </c>
-      <c r="D6" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>520</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TOH</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="n">
-        <v>360</v>
-      </c>
-      <c r="D8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>UTG</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>400</v>
-      </c>
-      <c r="D9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ØG</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>320</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>